--- a/Result/profitability/3521.xlsx
+++ b/Result/profitability/3521.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05999999999999993</v>
+        <v>0.1187499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-26.39</v>
+        <v>-26.875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.31</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08249999999999993</v>
+        <v>0.1987499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-24.99375</v>
+        <v>-8.876249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.37</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1549999999999999</v>
+        <v>0.1924999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.1675</v>
+        <v>-2.64125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1862499999999999</v>
+        <v>0.1649999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3650000000000002</v>
+        <v>-4.87875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1437499999999999</v>
+        <v>0.1149999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.235</v>
+        <v>-3.4375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08124999999999992</v>
+        <v>0.09499999999999992</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.24125</v>
+        <v>3.443750000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03124999999999992</v>
+        <v>-0.2362500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>3.92625</v>
+        <v>8.911250000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.3750000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>7.01</v>
+        <v>7.010000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>-0.5375000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>3.63</v>
+        <v>3.630000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3521</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1624.33%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.07124999999999992</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-28.8725</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.009433962264151</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.9352720450281427</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.133333333333333</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-36.11</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.082758620689655</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
